--- a/src/data/events_template.xlsx
+++ b/src/data/events_template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="252">
   <si>
     <t>Field</t>
   </si>
@@ -714,10 +714,22 @@
     <t>https://events.humanitix.com/meet-the-startups-susmi-x-sudata-x-sul-x-medscisoc</t>
   </si>
   <si>
-    <t>Datathon</t>
-  </si>
-  <si>
-    <t>SUDATA, COMM-STEM, SYNCS</t>
+    <t>Data-Hack</t>
+  </si>
+  <si>
+    <t>18/04/2026 to 20/04/2026</t>
+  </si>
+  <si>
+    <t>9am on 18th to 5pm on 20th</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-day datathon competition. Solve real-world data problems and win prizes! </t>
+  </si>
+  <si>
+    <t>SUDATA, COMM-STEM</t>
+  </si>
+  <si>
+    <t>https://events.humanitix.com/sudata-x-comms-stem-hackathon-2026</t>
   </si>
   <si>
     <t>Amstelveen Consulting Workshop</t>
@@ -763,6 +775,24 @@
   </si>
   <si>
     <t>https://docs.google.com/forms/d/e/1FAIpQLSe0fgyAoK7WviXjjQG5-B0WpO6OdeasQA5FbJU1cbfgnZAceQ/viewform</t>
+  </si>
+  <si>
+    <t>10:AM</t>
+  </si>
+  <si>
+    <t>Academic</t>
+  </si>
+  <si>
+    <t>Form a team to tackle real-world datasets to build innovative solutions to complex business problems. Extract insights, develop models, and get the opportunity to pitch your ideas in front of industry &amp; faculty judges.</t>
+  </si>
+  <si>
+    <t>SUDATA, Comm-STEM</t>
+  </si>
+  <si>
+    <t>Food provided throughout event</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/forms/d/e/1FAIpQLSc0PpmEPPKaErDartdzL0OhFWrcmmq79hsq49oZ7CR2hDUi9A/viewform?fbclid=PAVERFWAQ9to9leHRuA2FlbQIxMABzcnRjBmFwcF9pZA8xMjQwMjQ1NzQyODc0MTQAAadqwtgGT7mqVE0qgxyPpec07vi01Z8i_ckhJkuwZor_kkiucx7tcICnCg-DEA_aem_-v1T0RahWKiznkVs0U-yVA&amp;pli=1</t>
   </si>
 </sst>
 </file>
@@ -774,7 +804,7 @@
     <numFmt numFmtId="165" formatCode="hh:mm"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="20">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -822,6 +852,12 @@
       <name val="-apple-system"/>
     </font>
     <font>
+      <u/>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -860,6 +896,20 @@
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="-apple-system"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -887,7 +937,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="33">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -933,41 +983,59 @@
     <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2785,7 +2853,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="26.63"/>
+    <col customWidth="1" min="1" max="1" width="35.88"/>
+    <col customWidth="1" min="2" max="2" width="21.25"/>
+    <col customWidth="1" min="3" max="3" width="23.25"/>
     <col customWidth="1" min="4" max="4" width="49.5"/>
     <col customWidth="1" min="5" max="5" width="13.88"/>
     <col customWidth="1" min="6" max="6" width="102.5"/>
@@ -3059,34 +3129,34 @@
       <c r="A10" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B10" s="13">
-        <v>46111.0</v>
+      <c r="B10" s="15" t="s">
+        <v>226</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>35</v>
+        <v>227</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>35</v>
+        <v>222</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>142</v>
+        <v>228</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>35</v>
+      <c r="I10" s="16" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B11" s="13">
         <v>46132.0</v>
@@ -3101,7 +3171,7 @@
         <v>15</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>71</v>
@@ -3115,7 +3185,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B12" s="13">
         <v>46146.0</v>
@@ -3133,7 +3203,7 @@
         <v>45</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>35</v>
@@ -3173,7 +3243,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B14" s="13">
         <v>46174.0</v>
@@ -3188,7 +3258,7 @@
         <v>15</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>32</v>
@@ -3201,96 +3271,125 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="s">
-        <v>233</v>
-      </c>
-      <c r="B15" s="16">
+      <c r="A15" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="B15" s="18">
         <v>46086.0</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="19">
         <v>0.7083333333333334</v>
       </c>
-      <c r="D15" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="E15" s="19" t="s">
+      <c r="D15" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="E15" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="F15" s="20" t="s">
-        <v>235</v>
-      </c>
-      <c r="G15" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="H15" s="21" t="s">
-        <v>237</v>
-      </c>
-      <c r="I15" s="22" t="s">
-        <v>238</v>
-      </c>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="15"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="15"/>
-      <c r="R15" s="15"/>
-      <c r="S15" s="15"/>
-      <c r="T15" s="15"/>
-      <c r="U15" s="15"/>
-      <c r="V15" s="15"/>
-      <c r="W15" s="15"/>
-      <c r="X15" s="15"/>
-      <c r="Y15" s="15"/>
-      <c r="Z15" s="15"/>
+      <c r="F15" s="22" t="s">
+        <v>239</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="H15" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="I15" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="17"/>
+      <c r="S15" s="17"/>
+      <c r="T15" s="17"/>
+      <c r="U15" s="17"/>
+      <c r="V15" s="17"/>
+      <c r="W15" s="17"/>
+      <c r="X15" s="17"/>
+      <c r="Y15" s="17"/>
+      <c r="Z15" s="17"/>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="s">
-        <v>239</v>
-      </c>
-      <c r="B16" s="16">
+      <c r="A16" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="B16" s="18">
         <v>46098.0</v>
       </c>
-      <c r="C16" s="23">
+      <c r="C16" s="25">
         <v>0.75</v>
       </c>
-      <c r="D16" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" s="19" t="s">
+      <c r="D16" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="24" t="s">
+      <c r="F16" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="G16" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="G16" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="H16" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="I16" s="26" t="s">
-        <v>241</v>
-      </c>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="15"/>
-      <c r="S16" s="15"/>
-      <c r="T16" s="15"/>
-      <c r="U16" s="15"/>
-      <c r="V16" s="15"/>
-      <c r="W16" s="15"/>
-      <c r="X16" s="15"/>
-      <c r="Y16" s="15"/>
-      <c r="Z16" s="15"/>
+      <c r="H16" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="28" t="s">
+        <v>245</v>
+      </c>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="17"/>
+      <c r="S16" s="17"/>
+      <c r="T16" s="17"/>
+      <c r="U16" s="17"/>
+      <c r="V16" s="17"/>
+      <c r="W16" s="17"/>
+      <c r="X16" s="17"/>
+      <c r="Y16" s="17"/>
+      <c r="Z16" s="17"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="s">
+        <v>225</v>
+      </c>
+      <c r="B17" s="30">
+        <v>46130.0</v>
+      </c>
+      <c r="C17" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="D17" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="E17" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="F17" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="G17" s="29" t="s">
+        <v>249</v>
+      </c>
+      <c r="H17" s="29" t="s">
+        <v>250</v>
+      </c>
+      <c r="I17" s="32" t="s">
+        <v>251</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3301,9 +3400,11 @@
     <hyperlink r:id="rId5" ref="I7"/>
     <hyperlink r:id="rId6" ref="I8"/>
     <hyperlink r:id="rId7" ref="I9"/>
-    <hyperlink r:id="rId8" ref="I15"/>
-    <hyperlink r:id="rId9" ref="I16"/>
+    <hyperlink r:id="rId8" ref="I10"/>
+    <hyperlink r:id="rId9" ref="I15"/>
+    <hyperlink r:id="rId10" ref="I16"/>
+    <hyperlink r:id="rId11" ref="I17"/>
   </hyperlinks>
-  <drawing r:id="rId10"/>
+  <drawing r:id="rId12"/>
 </worksheet>
 </file>
--- a/src/data/events_template.xlsx
+++ b/src/data/events_template.xlsx
@@ -1,19 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/PengOlivia/Desktop/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2646D32-B9B1-6041-BB3C-C8E5A8294804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="18000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Instructions" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Events 2025" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Events 2026" sheetId="3" r:id="rId7"/>
+    <sheet name="Instructions" sheetId="1" r:id="rId1"/>
+    <sheet name="Events 2025" sheetId="2" r:id="rId2"/>
+    <sheet name="Events 2026" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="252">
   <si>
     <t>Field</t>
   </si>
@@ -587,10 +596,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://docs.google.com/forms/d/e/1FAIpQLSeduhevat2fDYJJUjY6mECZbH3QXoC_0hNrDCHVqyYdwnAiqg/viewform?usp=dialog</t>
     </r>
@@ -610,10 +619,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://docs.google.com/forms/d/e/1FAIpQLScKZVKDVWMbtH2mYJpaJJOdHb3vRpJby2CYVKwQ4UcD3wUGBg/viewform</t>
     </r>
@@ -693,10 +702,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://docs.google.com/forms/d/e/1FAIpQLScgW3fZhxdtB65OgVPNcWrCGxCODn6fjWnh4lLI3cafpXfg_A/viewform</t>
     </r>
@@ -714,70 +723,55 @@
     <t>https://events.humanitix.com/meet-the-startups-susmi-x-sudata-x-sul-x-medscisoc</t>
   </si>
   <si>
+    <t>Amstelveen Consulting Workshop</t>
+  </si>
+  <si>
+    <t>Consulting workshop and short case competition practice in collaboration with Amstelveen</t>
+  </si>
+  <si>
+    <t>Data Science Careers Panel</t>
+  </si>
+  <si>
+    <t>SUDATA, 180 Degrees</t>
+  </si>
+  <si>
+    <t>DATA1001/2001 Revision Session</t>
+  </si>
+  <si>
+    <t>STUVAC revision session for DATA1001 and DATA2001 final exam preparation.</t>
+  </si>
+  <si>
+    <t>Dinner with Jane Street</t>
+  </si>
+  <si>
+    <t>TBA University of Sydney</t>
+  </si>
+  <si>
+    <t>Jane Street is hosting a dinner in Sydney! University of Sydney students of all backgrounds and tenures are encouraged to attend. We hope to meet intellectually curious problem solvers - you don't need experience in finance to work at Jane Street.</t>
+  </si>
+  <si>
+    <t>SUDATA, Jane Street</t>
+  </si>
+  <si>
+    <t>Dinner</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/forms/d/e/1FAIpQLSf46ZiUBv2E_YBmU0tA3ywnUhGT7KrWh1ifW98jJ2F-iPxs4g/viewform</t>
+  </si>
+  <si>
+    <t>Jane Street Tech Talk</t>
+  </si>
+  <si>
+    <t>Join a JS technologist to learn more about “Making OCaml Safe for Performance Engineering.</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/forms/d/e/1FAIpQLSe0fgyAoK7WviXjjQG5-B0WpO6OdeasQA5FbJU1cbfgnZAceQ/viewform</t>
+  </si>
+  <si>
     <t>Data-Hack</t>
   </si>
   <si>
-    <t>18/04/2026 to 20/04/2026</t>
-  </si>
-  <si>
-    <t>9am on 18th to 5pm on 20th</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-day datathon competition. Solve real-world data problems and win prizes! </t>
-  </si>
-  <si>
-    <t>SUDATA, COMM-STEM</t>
-  </si>
-  <si>
-    <t>https://events.humanitix.com/sudata-x-comms-stem-hackathon-2026</t>
-  </si>
-  <si>
-    <t>Amstelveen Consulting Workshop</t>
-  </si>
-  <si>
-    <t>Consulting workshop and short case competition practice in collaboration with Amstelveen</t>
-  </si>
-  <si>
-    <t>Data Science Careers Panel</t>
-  </si>
-  <si>
-    <t>SUDATA, 180 Degrees</t>
-  </si>
-  <si>
-    <t>DATA1001/2001 Revision Session</t>
-  </si>
-  <si>
-    <t>STUVAC revision session for DATA1001 and DATA2001 final exam preparation.</t>
-  </si>
-  <si>
-    <t>Dinner with Jane Street</t>
-  </si>
-  <si>
-    <t>TBA University of Sydney</t>
-  </si>
-  <si>
-    <t>Jane Street is hosting a dinner in Sydney! University of Sydney students of all backgrounds and tenures are encouraged to attend. We hope to meet intellectually curious problem solvers - you don't need experience in finance to work at Jane Street.</t>
-  </si>
-  <si>
-    <t>SUDATA, Jane Street</t>
-  </si>
-  <si>
-    <t>Dinner</t>
-  </si>
-  <si>
-    <t>https://docs.google.com/forms/d/e/1FAIpQLSf46ZiUBv2E_YBmU0tA3ywnUhGT7KrWh1ifW98jJ2F-iPxs4g/viewform</t>
-  </si>
-  <si>
-    <t>Jane Street Tech Talk</t>
-  </si>
-  <si>
-    <t>Join a JS technologist to learn more about “Making OCaml Safe for Performance Engineering.</t>
-  </si>
-  <si>
-    <t>https://docs.google.com/forms/d/e/1FAIpQLSe0fgyAoK7WviXjjQG5-B0WpO6OdeasQA5FbJU1cbfgnZAceQ/viewform</t>
-  </si>
-  <si>
-    <t>10:AM</t>
+    <t>10:))AM</t>
   </si>
   <si>
     <t>Academic</t>
@@ -793,122 +787,163 @@
   </si>
   <si>
     <t>https://docs.google.com/forms/d/e/1FAIpQLSc0PpmEPPKaErDartdzL0OhFWrcmmq79hsq49oZ7CR2hDUi9A/viewform?fbclid=PAVERFWAQ9to9leHRuA2FlbQIxMABzcnRjBmFwcF9pZA8xMjQwMjQ1NzQyODc0MTQAAadqwtgGT7mqVE0qgxyPpec07vi01Z8i_ckhJkuwZor_kkiucx7tcICnCg-DEA_aem_-v1T0RahWKiznkVs0U-yVA&amp;pli=1</t>
+  </si>
+  <si>
+    <t>“The Way In” Seminar</t>
+  </si>
+  <si>
+    <t>Belinda Hutchinson Building 2150</t>
+  </si>
+  <si>
+    <t>“The Way In” is a career-focused seminar hosted by Seafaring Vane Edu designed to help students better understand how to break into data science and related STEM careers. The session will feature analysts and professionals working in the data space who will share practical insights into internship and graduate recruitment, including how they approached applications, what employers look for, and what students can do to improve their chances.</t>
+  </si>
+  <si>
+    <t>Food provided</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/forms/d/e/1FAIpQLSeBL6YgXO_7Cx990dXxaGKGehaZlJzeo6zFFGkYZ5rLoTWucQ/viewform?usp=dialog</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="hh:mm"/>
-    <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF0C1014"/>
       <name val="-apple-system"/>
     </font>
     <font>
-      <u/>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF1F1F1F"/>
       <name val="Docs-Roboto"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF1F1F1F"/>
       <name val="Roboto"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF1155CC"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="-apple-system"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF1155CC"/>
+      <name val="Calibri, sans-serif"/>
     </font>
   </fonts>
   <fills count="4">
@@ -916,7 +951,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -932,137 +967,79 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="30">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="17" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1252,22 +1229,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.75"/>
-    <col customWidth="1" min="2" max="2" width="38.25"/>
-    <col customWidth="1" min="3" max="3" width="22.88"/>
+    <col min="1" max="1" width="10.6640625" customWidth="1"/>
+    <col min="2" max="2" width="38.1640625" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1278,7 +1258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1289,7 +1269,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1297,10 +1277,10 @@
         <v>7</v>
       </c>
       <c r="C3" s="3">
-        <v>45731.0</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>45731</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1311,7 +1291,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1322,7 +1302,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -1333,7 +1313,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
@@ -1344,7 +1324,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
@@ -1355,7 +1335,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
@@ -1366,7 +1346,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
         <v>25</v>
       </c>
@@ -1379,28 +1359,29 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="C10"/>
+    <hyperlink ref="C10" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:I48"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="32.25"/>
-    <col customWidth="1" min="4" max="4" width="36.0"/>
-    <col customWidth="1" min="6" max="6" width="186.25"/>
-    <col customWidth="1" min="7" max="7" width="41.5"/>
-    <col customWidth="1" min="8" max="8" width="16.0"/>
-    <col customWidth="1" min="9" max="9" width="88.88"/>
+    <col min="1" max="1" width="32.1640625" customWidth="1"/>
+    <col min="4" max="4" width="36" customWidth="1"/>
+    <col min="6" max="6" width="186.1640625" customWidth="1"/>
+    <col min="7" max="7" width="41.5" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="88.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1429,15 +1410,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B2" s="3">
-        <v>45708.0</v>
+        <v>45708</v>
       </c>
       <c r="C2" s="4">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>29</v>
@@ -1458,12 +1439,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="3">
-        <v>45713.0</v>
+        <v>45713</v>
       </c>
       <c r="C3" s="4">
         <v>0.75</v>
@@ -1487,15 +1468,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>45713.0</v>
+        <v>45713</v>
       </c>
       <c r="C4" s="4">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>35</v>
@@ -1516,15 +1497,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B5" s="3">
-        <v>45719.0</v>
+        <v>45719</v>
       </c>
       <c r="C5" s="4">
-        <v>0.7083333333333334</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>35</v>
@@ -1545,12 +1526,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B6" s="3">
-        <v>45727.0</v>
+        <v>45727</v>
       </c>
       <c r="C6" s="4">
         <v>0.75</v>
@@ -1574,15 +1555,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B7" s="3">
-        <v>45729.0</v>
+        <v>45729</v>
       </c>
       <c r="C7" s="4">
-        <v>0.5833333333333334</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>35</v>
@@ -1603,12 +1584,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B8" s="3">
-        <v>45730.0</v>
+        <v>45730</v>
       </c>
       <c r="C8" s="4">
         <v>0.75</v>
@@ -1632,12 +1613,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B9" s="3">
-        <v>45733.0</v>
+        <v>45733</v>
       </c>
       <c r="C9" s="4">
         <v>0.375</v>
@@ -1661,12 +1642,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B10" s="3">
-        <v>45735.0</v>
+        <v>45735</v>
       </c>
       <c r="C10" s="4">
         <v>0.375</v>
@@ -1690,12 +1671,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B11" s="3">
-        <v>45743.0</v>
+        <v>45743</v>
       </c>
       <c r="C11" s="4">
         <v>0.75</v>
@@ -1719,12 +1700,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
         <v>66</v>
       </c>
       <c r="B12" s="3">
-        <v>45748.0</v>
+        <v>45748</v>
       </c>
       <c r="C12" s="4">
         <v>0.75</v>
@@ -1748,12 +1729,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
         <v>69</v>
       </c>
       <c r="B13" s="3">
-        <v>45754.0</v>
+        <v>45754</v>
       </c>
       <c r="C13" s="4">
         <v>0.625</v>
@@ -1777,12 +1758,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B14" s="3">
-        <v>45761.0</v>
+        <v>45761</v>
       </c>
       <c r="C14" s="4">
         <v>0.625</v>
@@ -1806,12 +1787,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
         <v>76</v>
       </c>
       <c r="B15" s="3">
-        <v>45775.0</v>
+        <v>45775</v>
       </c>
       <c r="C15" s="4">
         <v>0.75</v>
@@ -1835,12 +1816,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
         <v>79</v>
       </c>
       <c r="B16" s="3">
-        <v>45779.0</v>
+        <v>45779</v>
       </c>
       <c r="C16" s="4">
         <v>0.75</v>
@@ -1864,12 +1845,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B17" s="3">
-        <v>45782.0</v>
+        <v>45782</v>
       </c>
       <c r="C17" s="4">
         <v>0.75</v>
@@ -1893,15 +1874,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
         <v>84</v>
       </c>
       <c r="B18" s="3">
-        <v>45786.0</v>
+        <v>45786</v>
       </c>
       <c r="C18" s="4">
-        <v>0.7916666666666666</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>85</v>
@@ -1922,12 +1903,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B19" s="3">
-        <v>45797.0</v>
+        <v>45797</v>
       </c>
       <c r="C19" s="4">
         <v>0.75</v>
@@ -1951,12 +1932,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:9">
       <c r="A20" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B20" s="3">
-        <v>45799.0</v>
+        <v>45799</v>
       </c>
       <c r="C20" s="4">
         <v>0.75</v>
@@ -1980,12 +1961,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B21" s="3">
-        <v>45811.0</v>
+        <v>45811</v>
       </c>
       <c r="C21" s="4">
         <v>0.75</v>
@@ -2009,15 +1990,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:9">
       <c r="A22" s="2" t="s">
         <v>95</v>
       </c>
       <c r="B22" s="3">
-        <v>45811.0</v>
+        <v>45811</v>
       </c>
       <c r="C22" s="4">
-        <v>0.7916666666666666</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>96</v>
@@ -2038,15 +2019,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:9">
       <c r="A23" s="2" t="s">
         <v>100</v>
       </c>
       <c r="B23" s="3">
-        <v>45873.0</v>
+        <v>45873</v>
       </c>
       <c r="C23" s="4">
-        <v>0.5833333333333334</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>35</v>
@@ -2067,15 +2048,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:9">
       <c r="A24" s="2" t="s">
         <v>103</v>
       </c>
       <c r="B24" s="3">
-        <v>45877.0</v>
+        <v>45877</v>
       </c>
       <c r="C24" s="4">
-        <v>0.7916666666666666</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>85</v>
@@ -2096,12 +2077,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:9">
       <c r="A25" s="2" t="s">
         <v>105</v>
       </c>
       <c r="B25" s="3">
-        <v>45881.0</v>
+        <v>45881</v>
       </c>
       <c r="C25" s="4">
         <v>0.75</v>
@@ -2125,12 +2106,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:9">
       <c r="A26" s="2" t="s">
         <v>108</v>
       </c>
       <c r="B26" s="3">
-        <v>45881.0</v>
+        <v>45881</v>
       </c>
       <c r="C26" s="4">
         <v>0.75</v>
@@ -2154,12 +2135,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:9">
       <c r="A27" s="2" t="s">
         <v>110</v>
       </c>
       <c r="B27" s="3">
-        <v>45883.0</v>
+        <v>45883</v>
       </c>
       <c r="C27" s="4">
         <v>0.75</v>
@@ -2183,15 +2164,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:9">
       <c r="A28" s="2" t="s">
         <v>113</v>
       </c>
       <c r="B28" s="3">
-        <v>45887.0</v>
+        <v>45887</v>
       </c>
       <c r="C28" s="4">
-        <v>0.7083333333333334</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>114</v>
@@ -2212,12 +2193,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:9">
       <c r="A29" s="2" t="s">
         <v>117</v>
       </c>
       <c r="B29" s="3">
-        <v>45890.0</v>
+        <v>45890</v>
       </c>
       <c r="C29" s="4">
         <v>0.75</v>
@@ -2241,12 +2222,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:9">
       <c r="A30" s="2" t="s">
         <v>121</v>
       </c>
       <c r="B30" s="3">
-        <v>45897.0</v>
+        <v>45897</v>
       </c>
       <c r="C30" s="4">
         <v>0.625</v>
@@ -2270,12 +2251,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:9">
       <c r="A31" s="2" t="s">
         <v>124</v>
       </c>
       <c r="B31" s="3">
-        <v>45897.0</v>
+        <v>45897</v>
       </c>
       <c r="C31" s="4">
         <v>0.75</v>
@@ -2299,12 +2280,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:9">
       <c r="A32" s="2" t="s">
         <v>127</v>
       </c>
       <c r="B32" s="3">
-        <v>45902.0</v>
+        <v>45902</v>
       </c>
       <c r="C32" s="4">
         <v>0.75</v>
@@ -2328,12 +2309,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:9">
       <c r="A33" s="2" t="s">
         <v>129</v>
       </c>
       <c r="B33" s="3">
-        <v>45905.0</v>
+        <v>45905</v>
       </c>
       <c r="C33" s="4">
         <v>0.625</v>
@@ -2357,12 +2338,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:9">
       <c r="A34" s="2" t="s">
         <v>131</v>
       </c>
       <c r="B34" s="3">
-        <v>45911.0</v>
+        <v>45911</v>
       </c>
       <c r="C34" s="4">
         <v>0.625</v>
@@ -2386,12 +2367,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:9">
       <c r="A35" s="2" t="s">
         <v>134</v>
       </c>
       <c r="B35" s="3">
-        <v>45911.0</v>
+        <v>45911</v>
       </c>
       <c r="C35" s="4">
         <v>0.75</v>
@@ -2415,12 +2396,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:9">
       <c r="A36" s="2" t="s">
         <v>136</v>
       </c>
       <c r="B36" s="3">
-        <v>45918.0</v>
+        <v>45918</v>
       </c>
       <c r="C36" s="4">
         <v>0.75</v>
@@ -2444,12 +2425,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:9">
       <c r="A37" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B37" s="3">
-        <v>45923.0</v>
+        <v>45923</v>
       </c>
       <c r="C37" s="4">
         <v>0.625</v>
@@ -2473,12 +2454,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:9">
       <c r="A38" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B38" s="3">
-        <v>45929.0</v>
+        <v>45929</v>
       </c>
       <c r="C38" s="4">
         <v>0.375</v>
@@ -2502,12 +2483,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:9">
       <c r="A39" s="2" t="s">
         <v>145</v>
       </c>
       <c r="B39" s="3">
-        <v>45943.0</v>
+        <v>45943</v>
       </c>
       <c r="C39" s="4">
         <v>0.5</v>
@@ -2531,12 +2512,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:9">
       <c r="A40" s="2" t="s">
         <v>150</v>
       </c>
       <c r="B40" s="3">
-        <v>45944.0</v>
+        <v>45944</v>
       </c>
       <c r="C40" s="4">
         <v>0.75</v>
@@ -2560,15 +2541,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:9">
       <c r="A41" s="2" t="s">
         <v>152</v>
       </c>
       <c r="B41" s="3">
-        <v>45945.0</v>
+        <v>45945</v>
       </c>
       <c r="C41" s="4">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>35</v>
@@ -2589,12 +2570,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:9">
       <c r="A42" s="2" t="s">
         <v>154</v>
       </c>
       <c r="B42" s="3">
-        <v>45947.0</v>
+        <v>45947</v>
       </c>
       <c r="C42" s="4">
         <v>0.75</v>
@@ -2618,15 +2599,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:9">
       <c r="A43" s="2" t="s">
         <v>157</v>
       </c>
       <c r="B43" s="3">
-        <v>45953.0</v>
+        <v>45953</v>
       </c>
       <c r="C43" s="4">
-        <v>0.7916666666666666</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>158</v>
@@ -2647,12 +2628,12 @@
         <v>162</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:9">
       <c r="A44" s="2" t="s">
         <v>163</v>
       </c>
       <c r="B44" s="3">
-        <v>45954.0</v>
+        <v>45954</v>
       </c>
       <c r="C44" s="4">
         <v>0.6875</v>
@@ -2676,12 +2657,12 @@
         <v>166</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:9">
       <c r="A45" s="2" t="s">
         <v>167</v>
       </c>
       <c r="B45" s="3">
-        <v>45958.0</v>
+        <v>45958</v>
       </c>
       <c r="C45" s="4">
         <v>0.75</v>
@@ -2705,15 +2686,15 @@
         <v>171</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:9">
       <c r="A46" s="2" t="s">
         <v>172</v>
       </c>
       <c r="B46" s="3">
-        <v>45960.0</v>
+        <v>45960</v>
       </c>
       <c r="C46" s="4">
-        <v>0.4583333333333333</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>173</v>
@@ -2734,15 +2715,15 @@
         <v>176</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:9">
       <c r="A47" s="2" t="s">
         <v>177</v>
       </c>
       <c r="B47" s="3">
-        <v>45961.0</v>
+        <v>45961</v>
       </c>
       <c r="C47" s="4">
-        <v>0.7916666666666666</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>178</v>
@@ -2763,15 +2744,15 @@
         <v>181</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:9">
       <c r="A48" s="2" t="s">
         <v>182</v>
       </c>
       <c r="B48" s="3">
-        <v>45974.0</v>
+        <v>45974</v>
       </c>
       <c r="C48" s="4">
-        <v>0.4583333333333333</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>183</v>
@@ -2794,77 +2775,78 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="I2"/>
-    <hyperlink r:id="rId2" ref="I3"/>
-    <hyperlink r:id="rId3" ref="I4"/>
-    <hyperlink r:id="rId4" ref="I5"/>
-    <hyperlink r:id="rId5" ref="I6"/>
-    <hyperlink r:id="rId6" ref="I7"/>
-    <hyperlink r:id="rId7" ref="I8"/>
-    <hyperlink r:id="rId8" ref="I9"/>
-    <hyperlink r:id="rId9" ref="I10"/>
-    <hyperlink r:id="rId10" ref="I11"/>
-    <hyperlink r:id="rId11" ref="I12"/>
-    <hyperlink r:id="rId12" ref="I13"/>
-    <hyperlink r:id="rId13" ref="I14"/>
-    <hyperlink r:id="rId14" ref="I15"/>
-    <hyperlink r:id="rId15" ref="I16"/>
-    <hyperlink r:id="rId16" ref="I17"/>
-    <hyperlink r:id="rId17" ref="I18"/>
-    <hyperlink r:id="rId18" ref="I19"/>
-    <hyperlink r:id="rId19" ref="I20"/>
-    <hyperlink r:id="rId20" ref="I21"/>
-    <hyperlink r:id="rId21" ref="I22"/>
-    <hyperlink r:id="rId22" ref="I23"/>
-    <hyperlink r:id="rId23" ref="I24"/>
-    <hyperlink r:id="rId24" ref="I25"/>
-    <hyperlink r:id="rId25" ref="I26"/>
-    <hyperlink r:id="rId26" ref="I27"/>
-    <hyperlink r:id="rId27" ref="I28"/>
-    <hyperlink r:id="rId28" ref="I29"/>
-    <hyperlink r:id="rId29" ref="I30"/>
-    <hyperlink r:id="rId30" ref="I31"/>
-    <hyperlink r:id="rId31" ref="I32"/>
-    <hyperlink r:id="rId32" ref="I33"/>
-    <hyperlink r:id="rId33" ref="I34"/>
-    <hyperlink r:id="rId34" ref="I35"/>
-    <hyperlink r:id="rId35" ref="I36"/>
-    <hyperlink r:id="rId36" ref="I37"/>
-    <hyperlink r:id="rId37" ref="I38"/>
-    <hyperlink r:id="rId38" ref="I39"/>
-    <hyperlink r:id="rId39" ref="I40"/>
-    <hyperlink r:id="rId40" ref="I41"/>
-    <hyperlink r:id="rId41" ref="I42"/>
-    <hyperlink r:id="rId42" ref="I43"/>
-    <hyperlink r:id="rId43" ref="I44"/>
-    <hyperlink r:id="rId44" ref="I45"/>
-    <hyperlink r:id="rId45" ref="I46"/>
-    <hyperlink r:id="rId46" ref="I47"/>
-    <hyperlink r:id="rId47" ref="I48"/>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="I3" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="I4" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="I5" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="I6" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="I7" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="I8" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
+    <hyperlink ref="I9" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
+    <hyperlink ref="I10" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
+    <hyperlink ref="I11" r:id="rId10" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
+    <hyperlink ref="I12" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
+    <hyperlink ref="I13" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
+    <hyperlink ref="I14" r:id="rId13" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
+    <hyperlink ref="I15" r:id="rId14" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
+    <hyperlink ref="I16" r:id="rId15" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
+    <hyperlink ref="I17" r:id="rId16" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
+    <hyperlink ref="I18" r:id="rId17" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
+    <hyperlink ref="I19" r:id="rId18" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
+    <hyperlink ref="I20" r:id="rId19" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
+    <hyperlink ref="I21" r:id="rId20" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
+    <hyperlink ref="I22" r:id="rId21" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
+    <hyperlink ref="I23" r:id="rId22" xr:uid="{00000000-0004-0000-0100-000015000000}"/>
+    <hyperlink ref="I24" r:id="rId23" xr:uid="{00000000-0004-0000-0100-000016000000}"/>
+    <hyperlink ref="I25" r:id="rId24" xr:uid="{00000000-0004-0000-0100-000017000000}"/>
+    <hyperlink ref="I26" r:id="rId25" xr:uid="{00000000-0004-0000-0100-000018000000}"/>
+    <hyperlink ref="I27" r:id="rId26" xr:uid="{00000000-0004-0000-0100-000019000000}"/>
+    <hyperlink ref="I28" r:id="rId27" xr:uid="{00000000-0004-0000-0100-00001A000000}"/>
+    <hyperlink ref="I29" r:id="rId28" xr:uid="{00000000-0004-0000-0100-00001B000000}"/>
+    <hyperlink ref="I30" r:id="rId29" xr:uid="{00000000-0004-0000-0100-00001C000000}"/>
+    <hyperlink ref="I31" r:id="rId30" xr:uid="{00000000-0004-0000-0100-00001D000000}"/>
+    <hyperlink ref="I32" r:id="rId31" xr:uid="{00000000-0004-0000-0100-00001E000000}"/>
+    <hyperlink ref="I33" r:id="rId32" xr:uid="{00000000-0004-0000-0100-00001F000000}"/>
+    <hyperlink ref="I34" r:id="rId33" xr:uid="{00000000-0004-0000-0100-000020000000}"/>
+    <hyperlink ref="I35" r:id="rId34" xr:uid="{00000000-0004-0000-0100-000021000000}"/>
+    <hyperlink ref="I36" r:id="rId35" xr:uid="{00000000-0004-0000-0100-000022000000}"/>
+    <hyperlink ref="I37" r:id="rId36" xr:uid="{00000000-0004-0000-0100-000023000000}"/>
+    <hyperlink ref="I38" r:id="rId37" xr:uid="{00000000-0004-0000-0100-000024000000}"/>
+    <hyperlink ref="I39" r:id="rId38" xr:uid="{00000000-0004-0000-0100-000025000000}"/>
+    <hyperlink ref="I40" r:id="rId39" xr:uid="{00000000-0004-0000-0100-000026000000}"/>
+    <hyperlink ref="I41" r:id="rId40" xr:uid="{00000000-0004-0000-0100-000027000000}"/>
+    <hyperlink ref="I42" r:id="rId41" xr:uid="{00000000-0004-0000-0100-000028000000}"/>
+    <hyperlink ref="I43" r:id="rId42" xr:uid="{00000000-0004-0000-0100-000029000000}"/>
+    <hyperlink ref="I44" r:id="rId43" xr:uid="{00000000-0004-0000-0100-00002A000000}"/>
+    <hyperlink ref="I45" r:id="rId44" xr:uid="{00000000-0004-0000-0100-00002B000000}"/>
+    <hyperlink ref="I46" r:id="rId45" xr:uid="{00000000-0004-0000-0100-00002C000000}"/>
+    <hyperlink ref="I47" r:id="rId46" xr:uid="{00000000-0004-0000-0100-00002D000000}"/>
+    <hyperlink ref="I48" r:id="rId47" xr:uid="{00000000-0004-0000-0100-00002E000000}"/>
   </hyperlinks>
-  <drawing r:id="rId48"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:Z18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="35.88"/>
-    <col customWidth="1" min="2" max="2" width="21.25"/>
-    <col customWidth="1" min="3" max="3" width="23.25"/>
-    <col customWidth="1" min="4" max="4" width="49.5"/>
-    <col customWidth="1" min="5" max="5" width="13.88"/>
-    <col customWidth="1" min="6" max="6" width="102.5"/>
-    <col customWidth="1" min="7" max="7" width="33.25"/>
-    <col customWidth="1" min="8" max="8" width="33.75"/>
-    <col customWidth="1" min="9" max="9" width="96.25"/>
+    <col min="1" max="1" width="35.83203125" customWidth="1"/>
+    <col min="2" max="2" width="21.1640625" customWidth="1"/>
+    <col min="3" max="3" width="23.1640625" customWidth="1"/>
+    <col min="4" max="4" width="49.5" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" customWidth="1"/>
+    <col min="6" max="6" width="102.5" customWidth="1"/>
+    <col min="7" max="7" width="33.1640625" customWidth="1"/>
+    <col min="8" max="8" width="33.6640625" customWidth="1"/>
+    <col min="9" max="9" width="96.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:26">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -2880,28 +2862,28 @@
       <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:26">
       <c r="A2" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B2" s="7">
-        <v>46072.0</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.5833333333333334</v>
+      <c r="B2" s="6">
+        <v>46072</v>
+      </c>
+      <c r="C2" s="7">
+        <v>0.58333333333333337</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>188</v>
@@ -2909,28 +2891,28 @@
       <c r="E2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="2" t="s">
         <v>189</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="8" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:26">
       <c r="A3" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B3" s="7">
-        <v>46079.0</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.7083333333333334</v>
+      <c r="B3" s="6">
+        <v>46079</v>
+      </c>
+      <c r="C3" s="7">
+        <v>0.70833333333333337</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>192</v>
@@ -2938,27 +2920,27 @@
       <c r="E3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="2" t="s">
         <v>193</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="8" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:26">
       <c r="A4" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B4" s="7">
-        <v>46086.0</v>
-      </c>
-      <c r="C4" s="8">
+      <c r="B4" s="6">
+        <v>46086</v>
+      </c>
+      <c r="C4" s="7">
         <v>0.5</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -2967,28 +2949,28 @@
       <c r="E4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="2" t="s">
         <v>198</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="2" t="s">
         <v>200</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:26">
       <c r="A5" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B5" s="7">
-        <v>46101.0</v>
+      <c r="B5" s="6">
+        <v>46101</v>
       </c>
       <c r="C5" s="4">
-        <v>0.7291666666666666</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>202</v>
@@ -2996,25 +2978,25 @@
       <c r="E5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="2" t="s">
         <v>203</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="9" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:26">
       <c r="A6" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B6" s="7">
-        <v>46108.0</v>
+      <c r="B6" s="6">
+        <v>46108</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>208</v>
@@ -3025,7 +3007,7 @@
       <c r="E6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="2" t="s">
         <v>210</v>
       </c>
       <c r="G6" s="2" t="s">
@@ -3034,19 +3016,19 @@
       <c r="H6" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="10" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:26">
       <c r="A7" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B7" s="13">
-        <v>46085.0</v>
+      <c r="B7" s="11">
+        <v>46085</v>
       </c>
       <c r="C7" s="4">
-        <v>0.7083333333333334</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>214</v>
@@ -3063,19 +3045,19 @@
       <c r="H7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="10" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:26">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="13">
-        <v>46086.0</v>
-      </c>
-      <c r="C8" s="8">
-        <v>0.6666666666666666</v>
+      <c r="B8" s="11">
+        <v>46086</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0.66666666666666663</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>35</v>
@@ -3092,21 +3074,21 @@
       <c r="H8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="8" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:26">
       <c r="A9" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B9" s="13">
-        <v>46101.0</v>
+      <c r="B9" s="11">
+        <v>46101</v>
       </c>
       <c r="C9" s="4">
         <v>0.75</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="12" t="s">
         <v>222</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -3121,45 +3103,45 @@
       <c r="H9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="9" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:26">
       <c r="A10" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>226</v>
+      <c r="B10" s="11">
+        <v>46132</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>227</v>
+        <v>35</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>222</v>
+        <v>35</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>229</v>
+        <v>71</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="I10" s="16" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>35</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26">
       <c r="A11" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B11" s="13">
-        <v>46132.0</v>
+        <v>227</v>
+      </c>
+      <c r="B11" s="11">
+        <v>46146</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>35</v>
@@ -3171,10 +3153,10 @@
         <v>15</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>232</v>
+        <v>45</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>71</v>
+        <v>228</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>35</v>
@@ -3183,12 +3165,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:26">
       <c r="A12" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="B12" s="13">
-        <v>46146.0</v>
+        <v>88</v>
+      </c>
+      <c r="B12" s="11">
+        <v>46160</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>35</v>
@@ -3200,24 +3182,24 @@
         <v>15</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>234</v>
+        <v>32</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:26">
       <c r="A13" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B13" s="13">
-        <v>46160.0</v>
+        <v>229</v>
+      </c>
+      <c r="B13" s="11">
+        <v>46174</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>35</v>
@@ -3229,182 +3211,185 @@
         <v>15</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>89</v>
+        <v>230</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:26">
+      <c r="A14" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="B14" s="14">
+        <v>46086</v>
+      </c>
+      <c r="C14" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="H14" s="18" t="s">
         <v>235</v>
       </c>
-      <c r="B14" s="13">
-        <v>46174.0</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="I14" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="13"/>
+      <c r="S14" s="13"/>
+      <c r="T14" s="13"/>
+      <c r="U14" s="13"/>
+      <c r="V14" s="13"/>
+      <c r="W14" s="13"/>
+      <c r="X14" s="13"/>
+      <c r="Y14" s="13"/>
+      <c r="Z14" s="13"/>
+    </row>
+    <row r="15" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A15" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="B15" s="14">
+        <v>46098</v>
+      </c>
+      <c r="C15" s="20">
+        <v>0.75</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="G14" s="2" t="s">
+      <c r="F15" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="H15" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13"/>
+      <c r="S15" s="13"/>
+      <c r="T15" s="13"/>
+      <c r="U15" s="13"/>
+      <c r="V15" s="13"/>
+      <c r="W15" s="13"/>
+      <c r="X15" s="13"/>
+      <c r="Y15" s="13"/>
+      <c r="Z15" s="13"/>
+    </row>
+    <row r="16" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A16" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="B16" s="25">
+        <v>46130</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>241</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>208</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="F16" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="G16" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="H16" s="24" t="s">
+        <v>245</v>
+      </c>
+      <c r="I16" s="27" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A17" s="24" t="s">
+        <v>247</v>
+      </c>
+      <c r="B17" s="28">
+        <v>46142</v>
+      </c>
+      <c r="C17" s="20">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="G17" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="B15" s="18">
-        <v>46086.0</v>
-      </c>
-      <c r="C15" s="19">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>238</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" s="22" t="s">
-        <v>239</v>
-      </c>
-      <c r="G15" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="H15" s="23" t="s">
-        <v>241</v>
-      </c>
-      <c r="I15" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="17"/>
-      <c r="S15" s="17"/>
-      <c r="T15" s="17"/>
-      <c r="U15" s="17"/>
-      <c r="V15" s="17"/>
-      <c r="W15" s="17"/>
-      <c r="X15" s="17"/>
-      <c r="Y15" s="17"/>
-      <c r="Z15" s="17"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="17" t="s">
-        <v>243</v>
-      </c>
-      <c r="B16" s="18">
-        <v>46098.0</v>
-      </c>
-      <c r="C16" s="25">
-        <v>0.75</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="G16" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="H16" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="I16" s="28" t="s">
-        <v>245</v>
-      </c>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="17"/>
-      <c r="S16" s="17"/>
-      <c r="T16" s="17"/>
-      <c r="U16" s="17"/>
-      <c r="V16" s="17"/>
-      <c r="W16" s="17"/>
-      <c r="X16" s="17"/>
-      <c r="Y16" s="17"/>
-      <c r="Z16" s="17"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="29" t="s">
-        <v>225</v>
-      </c>
-      <c r="B17" s="30">
-        <v>46130.0</v>
-      </c>
-      <c r="C17" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="D17" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="E17" s="29" t="s">
-        <v>247</v>
-      </c>
-      <c r="F17" s="31" t="s">
-        <v>248</v>
-      </c>
-      <c r="G17" s="29" t="s">
-        <v>249</v>
-      </c>
-      <c r="H17" s="29" t="s">
+      <c r="H17" s="24" t="s">
         <v>250</v>
       </c>
-      <c r="I17" s="32" t="s">
+      <c r="I17" s="29" t="s">
         <v>251</v>
       </c>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" customHeight="1">
+      <c r="F18" s="17"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="I2"/>
-    <hyperlink r:id="rId2" ref="I3"/>
-    <hyperlink r:id="rId3" ref="I5"/>
-    <hyperlink r:id="rId4" ref="I6"/>
-    <hyperlink r:id="rId5" ref="I7"/>
-    <hyperlink r:id="rId6" ref="I8"/>
-    <hyperlink r:id="rId7" ref="I9"/>
-    <hyperlink r:id="rId8" ref="I10"/>
-    <hyperlink r:id="rId9" ref="I15"/>
-    <hyperlink r:id="rId10" ref="I16"/>
-    <hyperlink r:id="rId11" ref="I17"/>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="I3" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="I5" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
+    <hyperlink ref="I6" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
+    <hyperlink ref="I7" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
+    <hyperlink ref="I8" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000005000000}"/>
+    <hyperlink ref="I9" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
+    <hyperlink ref="I14" r:id="rId8" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
+    <hyperlink ref="I15" r:id="rId9" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
+    <hyperlink ref="I16" r:id="rId10" xr:uid="{00000000-0004-0000-0200-000009000000}"/>
+    <hyperlink ref="I17" r:id="rId11" xr:uid="{00000000-0004-0000-0200-00000A000000}"/>
   </hyperlinks>
-  <drawing r:id="rId12"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/data/events_template.xlsx
+++ b/src/data/events_template.xlsx
@@ -1,28 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/PengOlivia/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2646D32-B9B1-6041-BB3C-C8E5A8294804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="18000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Instructions" sheetId="1" r:id="rId1"/>
-    <sheet name="Events 2025" sheetId="2" r:id="rId2"/>
-    <sheet name="Events 2026" sheetId="3" r:id="rId3"/>
+    <sheet state="visible" name="Instructions" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Events 2025" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Events 2026" sheetId="3" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="246">
   <si>
     <t>Field</t>
   </si>
@@ -596,10 +587,10 @@
   <si>
     <r>
       <rPr>
+        <rFont val="Calibri, sans-serif"/>
+        <color rgb="FF1155CC"/>
+        <sz val="11.0"/>
         <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
       </rPr>
       <t>https://docs.google.com/forms/d/e/1FAIpQLSeduhevat2fDYJJUjY6mECZbH3QXoC_0hNrDCHVqyYdwnAiqg/viewform?usp=dialog</t>
     </r>
@@ -619,10 +610,10 @@
   <si>
     <r>
       <rPr>
+        <rFont val="Calibri, sans-serif"/>
+        <color rgb="FF1155CC"/>
+        <sz val="11.0"/>
         <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
       </rPr>
       <t>https://docs.google.com/forms/d/e/1FAIpQLScKZVKDVWMbtH2mYJpaJJOdHb3vRpJby2CYVKwQ4UcD3wUGBg/viewform</t>
     </r>
@@ -702,10 +693,10 @@
   <si>
     <r>
       <rPr>
+        <rFont val="Calibri, sans-serif"/>
+        <color rgb="FF1155CC"/>
+        <sz val="11.0"/>
         <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
       </rPr>
       <t>https://docs.google.com/forms/d/e/1FAIpQLScgW3fZhxdtB65OgVPNcWrCGxCODn6fjWnh4lLI3cafpXfg_A/viewform</t>
     </r>
@@ -771,9 +762,6 @@
     <t>Data-Hack</t>
   </si>
   <si>
-    <t>10:))AM</t>
-  </si>
-  <si>
     <t>Academic</t>
   </si>
   <si>
@@ -787,163 +775,116 @@
   </si>
   <si>
     <t>https://docs.google.com/forms/d/e/1FAIpQLSc0PpmEPPKaErDartdzL0OhFWrcmmq79hsq49oZ7CR2hDUi9A/viewform?fbclid=PAVERFWAQ9to9leHRuA2FlbQIxMABzcnRjBmFwcF9pZA8xMjQwMjQ1NzQyODc0MTQAAadqwtgGT7mqVE0qgxyPpec07vi01Z8i_ckhJkuwZor_kkiucx7tcICnCg-DEA_aem_-v1T0RahWKiznkVs0U-yVA&amp;pli=1</t>
-  </si>
-  <si>
-    <t>“The Way In” Seminar</t>
-  </si>
-  <si>
-    <t>Belinda Hutchinson Building 2150</t>
-  </si>
-  <si>
-    <t>“The Way In” is a career-focused seminar hosted by Seafaring Vane Edu designed to help students better understand how to break into data science and related STEM careers. The session will feature analysts and professionals working in the data space who will share practical insights into internship and graduate recruitment, including how they approached applications, what employers look for, and what students can do to improve their chances.</t>
-  </si>
-  <si>
-    <t>Food provided</t>
-  </si>
-  <si>
-    <t>https://docs.google.com/forms/d/e/1FAIpQLSeBL6YgXO_7Cx990dXxaGKGehaZlJzeo6zFFGkYZ5rLoTWucQ/viewform?usp=dialog</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="hh:mm"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="19">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF0C1014"/>
       <name val="-apple-system"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF1F1F1F"/>
       <name val="Docs-Roboto"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF1F1F1F"/>
       <name val="Roboto"/>
     </font>
     <font>
       <u/>
-      <sz val="10"/>
       <color rgb="FF1155CC"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="-apple-system"/>
     </font>
     <font>
       <u/>
-      <sz val="10"/>
       <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF1155CC"/>
-      <name val="Calibri, sans-serif"/>
     </font>
   </fonts>
   <fills count="4">
@@ -951,7 +892,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -967,79 +908,135 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="30">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+  <cellXfs count="33">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="16" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="16" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1229,25 +1226,22 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" customWidth="1"/>
-    <col min="2" max="2" width="38.1640625" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="10.75"/>
+    <col customWidth="1" min="2" max="2" width="38.25"/>
+    <col customWidth="1" min="3" max="3" width="22.88"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1258,7 +1252,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1269,7 +1263,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1277,10 +1271,10 @@
         <v>7</v>
       </c>
       <c r="C3" s="3">
-        <v>45731</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>45731.0</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1291,7 +1285,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1302,7 +1296,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -1313,7 +1307,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
@@ -1324,7 +1318,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8">
       <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
@@ -1335,7 +1329,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9">
       <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
@@ -1346,7 +1340,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10">
       <c r="A10" s="2" t="s">
         <v>25</v>
       </c>
@@ -1359,29 +1353,28 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C10" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink r:id="rId1" ref="C10"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="32.1640625" customWidth="1"/>
-    <col min="4" max="4" width="36" customWidth="1"/>
-    <col min="6" max="6" width="186.1640625" customWidth="1"/>
-    <col min="7" max="7" width="41.5" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="88.83203125" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="32.25"/>
+    <col customWidth="1" min="4" max="4" width="36.0"/>
+    <col customWidth="1" min="6" max="6" width="186.25"/>
+    <col customWidth="1" min="7" max="7" width="41.5"/>
+    <col customWidth="1" min="8" max="8" width="16.0"/>
+    <col customWidth="1" min="9" max="9" width="88.88"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1410,15 +1403,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2">
       <c r="A2" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B2" s="3">
-        <v>45708</v>
+        <v>45708.0</v>
       </c>
       <c r="C2" s="4">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>29</v>
@@ -1439,12 +1432,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="3">
-        <v>45713</v>
+        <v>45713.0</v>
       </c>
       <c r="C3" s="4">
         <v>0.75</v>
@@ -1468,15 +1461,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4">
       <c r="A4" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>45713</v>
+        <v>45713.0</v>
       </c>
       <c r="C4" s="4">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>35</v>
@@ -1497,15 +1490,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5">
       <c r="A5" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B5" s="3">
-        <v>45719</v>
+        <v>45719.0</v>
       </c>
       <c r="C5" s="4">
-        <v>0.70833333333333337</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>35</v>
@@ -1526,12 +1519,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6">
       <c r="A6" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B6" s="3">
-        <v>45727</v>
+        <v>45727.0</v>
       </c>
       <c r="C6" s="4">
         <v>0.75</v>
@@ -1555,15 +1548,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7">
       <c r="A7" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B7" s="3">
-        <v>45729</v>
+        <v>45729.0</v>
       </c>
       <c r="C7" s="4">
-        <v>0.58333333333333337</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>35</v>
@@ -1584,12 +1577,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8">
       <c r="A8" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B8" s="3">
-        <v>45730</v>
+        <v>45730.0</v>
       </c>
       <c r="C8" s="4">
         <v>0.75</v>
@@ -1613,12 +1606,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9">
       <c r="A9" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B9" s="3">
-        <v>45733</v>
+        <v>45733.0</v>
       </c>
       <c r="C9" s="4">
         <v>0.375</v>
@@ -1642,12 +1635,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10">
       <c r="A10" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B10" s="3">
-        <v>45735</v>
+        <v>45735.0</v>
       </c>
       <c r="C10" s="4">
         <v>0.375</v>
@@ -1671,12 +1664,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11">
       <c r="A11" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B11" s="3">
-        <v>45743</v>
+        <v>45743.0</v>
       </c>
       <c r="C11" s="4">
         <v>0.75</v>
@@ -1700,12 +1693,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12">
       <c r="A12" s="2" t="s">
         <v>66</v>
       </c>
       <c r="B12" s="3">
-        <v>45748</v>
+        <v>45748.0</v>
       </c>
       <c r="C12" s="4">
         <v>0.75</v>
@@ -1729,12 +1722,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13">
       <c r="A13" s="2" t="s">
         <v>69</v>
       </c>
       <c r="B13" s="3">
-        <v>45754</v>
+        <v>45754.0</v>
       </c>
       <c r="C13" s="4">
         <v>0.625</v>
@@ -1758,12 +1751,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14">
       <c r="A14" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B14" s="3">
-        <v>45761</v>
+        <v>45761.0</v>
       </c>
       <c r="C14" s="4">
         <v>0.625</v>
@@ -1787,12 +1780,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15">
       <c r="A15" s="2" t="s">
         <v>76</v>
       </c>
       <c r="B15" s="3">
-        <v>45775</v>
+        <v>45775.0</v>
       </c>
       <c r="C15" s="4">
         <v>0.75</v>
@@ -1816,12 +1809,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16">
       <c r="A16" s="2" t="s">
         <v>79</v>
       </c>
       <c r="B16" s="3">
-        <v>45779</v>
+        <v>45779.0</v>
       </c>
       <c r="C16" s="4">
         <v>0.75</v>
@@ -1845,12 +1838,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17">
       <c r="A17" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B17" s="3">
-        <v>45782</v>
+        <v>45782.0</v>
       </c>
       <c r="C17" s="4">
         <v>0.75</v>
@@ -1874,15 +1867,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18">
       <c r="A18" s="2" t="s">
         <v>84</v>
       </c>
       <c r="B18" s="3">
-        <v>45786</v>
+        <v>45786.0</v>
       </c>
       <c r="C18" s="4">
-        <v>0.79166666666666663</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>85</v>
@@ -1903,12 +1896,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19">
       <c r="A19" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B19" s="3">
-        <v>45797</v>
+        <v>45797.0</v>
       </c>
       <c r="C19" s="4">
         <v>0.75</v>
@@ -1932,12 +1925,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20">
       <c r="A20" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B20" s="3">
-        <v>45799</v>
+        <v>45799.0</v>
       </c>
       <c r="C20" s="4">
         <v>0.75</v>
@@ -1961,12 +1954,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21">
       <c r="A21" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B21" s="3">
-        <v>45811</v>
+        <v>45811.0</v>
       </c>
       <c r="C21" s="4">
         <v>0.75</v>
@@ -1990,15 +1983,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22">
       <c r="A22" s="2" t="s">
         <v>95</v>
       </c>
       <c r="B22" s="3">
-        <v>45811</v>
+        <v>45811.0</v>
       </c>
       <c r="C22" s="4">
-        <v>0.79166666666666663</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>96</v>
@@ -2019,15 +2012,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23">
       <c r="A23" s="2" t="s">
         <v>100</v>
       </c>
       <c r="B23" s="3">
-        <v>45873</v>
+        <v>45873.0</v>
       </c>
       <c r="C23" s="4">
-        <v>0.58333333333333337</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>35</v>
@@ -2048,15 +2041,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24">
       <c r="A24" s="2" t="s">
         <v>103</v>
       </c>
       <c r="B24" s="3">
-        <v>45877</v>
+        <v>45877.0</v>
       </c>
       <c r="C24" s="4">
-        <v>0.79166666666666663</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>85</v>
@@ -2077,12 +2070,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25">
       <c r="A25" s="2" t="s">
         <v>105</v>
       </c>
       <c r="B25" s="3">
-        <v>45881</v>
+        <v>45881.0</v>
       </c>
       <c r="C25" s="4">
         <v>0.75</v>
@@ -2106,12 +2099,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26">
       <c r="A26" s="2" t="s">
         <v>108</v>
       </c>
       <c r="B26" s="3">
-        <v>45881</v>
+        <v>45881.0</v>
       </c>
       <c r="C26" s="4">
         <v>0.75</v>
@@ -2135,12 +2128,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27">
       <c r="A27" s="2" t="s">
         <v>110</v>
       </c>
       <c r="B27" s="3">
-        <v>45883</v>
+        <v>45883.0</v>
       </c>
       <c r="C27" s="4">
         <v>0.75</v>
@@ -2164,15 +2157,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28">
       <c r="A28" s="2" t="s">
         <v>113</v>
       </c>
       <c r="B28" s="3">
-        <v>45887</v>
+        <v>45887.0</v>
       </c>
       <c r="C28" s="4">
-        <v>0.70833333333333337</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>114</v>
@@ -2193,12 +2186,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29">
       <c r="A29" s="2" t="s">
         <v>117</v>
       </c>
       <c r="B29" s="3">
-        <v>45890</v>
+        <v>45890.0</v>
       </c>
       <c r="C29" s="4">
         <v>0.75</v>
@@ -2222,12 +2215,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30">
       <c r="A30" s="2" t="s">
         <v>121</v>
       </c>
       <c r="B30" s="3">
-        <v>45897</v>
+        <v>45897.0</v>
       </c>
       <c r="C30" s="4">
         <v>0.625</v>
@@ -2251,12 +2244,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31">
       <c r="A31" s="2" t="s">
         <v>124</v>
       </c>
       <c r="B31" s="3">
-        <v>45897</v>
+        <v>45897.0</v>
       </c>
       <c r="C31" s="4">
         <v>0.75</v>
@@ -2280,12 +2273,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32">
       <c r="A32" s="2" t="s">
         <v>127</v>
       </c>
       <c r="B32" s="3">
-        <v>45902</v>
+        <v>45902.0</v>
       </c>
       <c r="C32" s="4">
         <v>0.75</v>
@@ -2309,12 +2302,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33">
       <c r="A33" s="2" t="s">
         <v>129</v>
       </c>
       <c r="B33" s="3">
-        <v>45905</v>
+        <v>45905.0</v>
       </c>
       <c r="C33" s="4">
         <v>0.625</v>
@@ -2338,12 +2331,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34">
       <c r="A34" s="2" t="s">
         <v>131</v>
       </c>
       <c r="B34" s="3">
-        <v>45911</v>
+        <v>45911.0</v>
       </c>
       <c r="C34" s="4">
         <v>0.625</v>
@@ -2367,12 +2360,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35">
       <c r="A35" s="2" t="s">
         <v>134</v>
       </c>
       <c r="B35" s="3">
-        <v>45911</v>
+        <v>45911.0</v>
       </c>
       <c r="C35" s="4">
         <v>0.75</v>
@@ -2396,12 +2389,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36">
       <c r="A36" s="2" t="s">
         <v>136</v>
       </c>
       <c r="B36" s="3">
-        <v>45918</v>
+        <v>45918.0</v>
       </c>
       <c r="C36" s="4">
         <v>0.75</v>
@@ -2425,12 +2418,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37">
       <c r="A37" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B37" s="3">
-        <v>45923</v>
+        <v>45923.0</v>
       </c>
       <c r="C37" s="4">
         <v>0.625</v>
@@ -2454,12 +2447,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38">
       <c r="A38" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B38" s="3">
-        <v>45929</v>
+        <v>45929.0</v>
       </c>
       <c r="C38" s="4">
         <v>0.375</v>
@@ -2483,12 +2476,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39">
       <c r="A39" s="2" t="s">
         <v>145</v>
       </c>
       <c r="B39" s="3">
-        <v>45943</v>
+        <v>45943.0</v>
       </c>
       <c r="C39" s="4">
         <v>0.5</v>
@@ -2512,12 +2505,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40">
       <c r="A40" s="2" t="s">
         <v>150</v>
       </c>
       <c r="B40" s="3">
-        <v>45944</v>
+        <v>45944.0</v>
       </c>
       <c r="C40" s="4">
         <v>0.75</v>
@@ -2541,15 +2534,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41">
       <c r="A41" s="2" t="s">
         <v>152</v>
       </c>
       <c r="B41" s="3">
-        <v>45945</v>
+        <v>45945.0</v>
       </c>
       <c r="C41" s="4">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>35</v>
@@ -2570,12 +2563,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42">
       <c r="A42" s="2" t="s">
         <v>154</v>
       </c>
       <c r="B42" s="3">
-        <v>45947</v>
+        <v>45947.0</v>
       </c>
       <c r="C42" s="4">
         <v>0.75</v>
@@ -2599,15 +2592,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43">
       <c r="A43" s="2" t="s">
         <v>157</v>
       </c>
       <c r="B43" s="3">
-        <v>45953</v>
+        <v>45953.0</v>
       </c>
       <c r="C43" s="4">
-        <v>0.79166666666666663</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>158</v>
@@ -2628,12 +2621,12 @@
         <v>162</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44">
       <c r="A44" s="2" t="s">
         <v>163</v>
       </c>
       <c r="B44" s="3">
-        <v>45954</v>
+        <v>45954.0</v>
       </c>
       <c r="C44" s="4">
         <v>0.6875</v>
@@ -2657,12 +2650,12 @@
         <v>166</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45">
       <c r="A45" s="2" t="s">
         <v>167</v>
       </c>
       <c r="B45" s="3">
-        <v>45958</v>
+        <v>45958.0</v>
       </c>
       <c r="C45" s="4">
         <v>0.75</v>
@@ -2686,15 +2679,15 @@
         <v>171</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46">
       <c r="A46" s="2" t="s">
         <v>172</v>
       </c>
       <c r="B46" s="3">
-        <v>45960</v>
+        <v>45960.0</v>
       </c>
       <c r="C46" s="4">
-        <v>0.45833333333333331</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>173</v>
@@ -2715,15 +2708,15 @@
         <v>176</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47">
       <c r="A47" s="2" t="s">
         <v>177</v>
       </c>
       <c r="B47" s="3">
-        <v>45961</v>
+        <v>45961.0</v>
       </c>
       <c r="C47" s="4">
-        <v>0.79166666666666663</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>178</v>
@@ -2744,15 +2737,15 @@
         <v>181</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48">
       <c r="A48" s="2" t="s">
         <v>182</v>
       </c>
       <c r="B48" s="3">
-        <v>45974</v>
+        <v>45974.0</v>
       </c>
       <c r="C48" s="4">
-        <v>0.45833333333333331</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>183</v>
@@ -2775,78 +2768,77 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="I3" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="I4" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
-    <hyperlink ref="I5" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
-    <hyperlink ref="I6" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
-    <hyperlink ref="I7" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
-    <hyperlink ref="I8" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
-    <hyperlink ref="I9" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
-    <hyperlink ref="I10" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
-    <hyperlink ref="I11" r:id="rId10" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
-    <hyperlink ref="I12" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
-    <hyperlink ref="I13" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
-    <hyperlink ref="I14" r:id="rId13" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
-    <hyperlink ref="I15" r:id="rId14" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
-    <hyperlink ref="I16" r:id="rId15" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
-    <hyperlink ref="I17" r:id="rId16" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
-    <hyperlink ref="I18" r:id="rId17" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
-    <hyperlink ref="I19" r:id="rId18" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
-    <hyperlink ref="I20" r:id="rId19" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
-    <hyperlink ref="I21" r:id="rId20" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
-    <hyperlink ref="I22" r:id="rId21" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
-    <hyperlink ref="I23" r:id="rId22" xr:uid="{00000000-0004-0000-0100-000015000000}"/>
-    <hyperlink ref="I24" r:id="rId23" xr:uid="{00000000-0004-0000-0100-000016000000}"/>
-    <hyperlink ref="I25" r:id="rId24" xr:uid="{00000000-0004-0000-0100-000017000000}"/>
-    <hyperlink ref="I26" r:id="rId25" xr:uid="{00000000-0004-0000-0100-000018000000}"/>
-    <hyperlink ref="I27" r:id="rId26" xr:uid="{00000000-0004-0000-0100-000019000000}"/>
-    <hyperlink ref="I28" r:id="rId27" xr:uid="{00000000-0004-0000-0100-00001A000000}"/>
-    <hyperlink ref="I29" r:id="rId28" xr:uid="{00000000-0004-0000-0100-00001B000000}"/>
-    <hyperlink ref="I30" r:id="rId29" xr:uid="{00000000-0004-0000-0100-00001C000000}"/>
-    <hyperlink ref="I31" r:id="rId30" xr:uid="{00000000-0004-0000-0100-00001D000000}"/>
-    <hyperlink ref="I32" r:id="rId31" xr:uid="{00000000-0004-0000-0100-00001E000000}"/>
-    <hyperlink ref="I33" r:id="rId32" xr:uid="{00000000-0004-0000-0100-00001F000000}"/>
-    <hyperlink ref="I34" r:id="rId33" xr:uid="{00000000-0004-0000-0100-000020000000}"/>
-    <hyperlink ref="I35" r:id="rId34" xr:uid="{00000000-0004-0000-0100-000021000000}"/>
-    <hyperlink ref="I36" r:id="rId35" xr:uid="{00000000-0004-0000-0100-000022000000}"/>
-    <hyperlink ref="I37" r:id="rId36" xr:uid="{00000000-0004-0000-0100-000023000000}"/>
-    <hyperlink ref="I38" r:id="rId37" xr:uid="{00000000-0004-0000-0100-000024000000}"/>
-    <hyperlink ref="I39" r:id="rId38" xr:uid="{00000000-0004-0000-0100-000025000000}"/>
-    <hyperlink ref="I40" r:id="rId39" xr:uid="{00000000-0004-0000-0100-000026000000}"/>
-    <hyperlink ref="I41" r:id="rId40" xr:uid="{00000000-0004-0000-0100-000027000000}"/>
-    <hyperlink ref="I42" r:id="rId41" xr:uid="{00000000-0004-0000-0100-000028000000}"/>
-    <hyperlink ref="I43" r:id="rId42" xr:uid="{00000000-0004-0000-0100-000029000000}"/>
-    <hyperlink ref="I44" r:id="rId43" xr:uid="{00000000-0004-0000-0100-00002A000000}"/>
-    <hyperlink ref="I45" r:id="rId44" xr:uid="{00000000-0004-0000-0100-00002B000000}"/>
-    <hyperlink ref="I46" r:id="rId45" xr:uid="{00000000-0004-0000-0100-00002C000000}"/>
-    <hyperlink ref="I47" r:id="rId46" xr:uid="{00000000-0004-0000-0100-00002D000000}"/>
-    <hyperlink ref="I48" r:id="rId47" xr:uid="{00000000-0004-0000-0100-00002E000000}"/>
+    <hyperlink r:id="rId1" ref="I2"/>
+    <hyperlink r:id="rId2" ref="I3"/>
+    <hyperlink r:id="rId3" ref="I4"/>
+    <hyperlink r:id="rId4" ref="I5"/>
+    <hyperlink r:id="rId5" ref="I6"/>
+    <hyperlink r:id="rId6" ref="I7"/>
+    <hyperlink r:id="rId7" ref="I8"/>
+    <hyperlink r:id="rId8" ref="I9"/>
+    <hyperlink r:id="rId9" ref="I10"/>
+    <hyperlink r:id="rId10" ref="I11"/>
+    <hyperlink r:id="rId11" ref="I12"/>
+    <hyperlink r:id="rId12" ref="I13"/>
+    <hyperlink r:id="rId13" ref="I14"/>
+    <hyperlink r:id="rId14" ref="I15"/>
+    <hyperlink r:id="rId15" ref="I16"/>
+    <hyperlink r:id="rId16" ref="I17"/>
+    <hyperlink r:id="rId17" ref="I18"/>
+    <hyperlink r:id="rId18" ref="I19"/>
+    <hyperlink r:id="rId19" ref="I20"/>
+    <hyperlink r:id="rId20" ref="I21"/>
+    <hyperlink r:id="rId21" ref="I22"/>
+    <hyperlink r:id="rId22" ref="I23"/>
+    <hyperlink r:id="rId23" ref="I24"/>
+    <hyperlink r:id="rId24" ref="I25"/>
+    <hyperlink r:id="rId25" ref="I26"/>
+    <hyperlink r:id="rId26" ref="I27"/>
+    <hyperlink r:id="rId27" ref="I28"/>
+    <hyperlink r:id="rId28" ref="I29"/>
+    <hyperlink r:id="rId29" ref="I30"/>
+    <hyperlink r:id="rId30" ref="I31"/>
+    <hyperlink r:id="rId31" ref="I32"/>
+    <hyperlink r:id="rId32" ref="I33"/>
+    <hyperlink r:id="rId33" ref="I34"/>
+    <hyperlink r:id="rId34" ref="I35"/>
+    <hyperlink r:id="rId35" ref="I36"/>
+    <hyperlink r:id="rId36" ref="I37"/>
+    <hyperlink r:id="rId37" ref="I38"/>
+    <hyperlink r:id="rId38" ref="I39"/>
+    <hyperlink r:id="rId39" ref="I40"/>
+    <hyperlink r:id="rId40" ref="I41"/>
+    <hyperlink r:id="rId41" ref="I42"/>
+    <hyperlink r:id="rId42" ref="I43"/>
+    <hyperlink r:id="rId43" ref="I44"/>
+    <hyperlink r:id="rId44" ref="I45"/>
+    <hyperlink r:id="rId45" ref="I46"/>
+    <hyperlink r:id="rId46" ref="I47"/>
+    <hyperlink r:id="rId47" ref="I48"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId48"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="35.83203125" customWidth="1"/>
-    <col min="2" max="2" width="21.1640625" customWidth="1"/>
-    <col min="3" max="3" width="23.1640625" customWidth="1"/>
-    <col min="4" max="4" width="49.5" customWidth="1"/>
-    <col min="5" max="5" width="13.83203125" customWidth="1"/>
-    <col min="6" max="6" width="102.5" customWidth="1"/>
-    <col min="7" max="7" width="33.1640625" customWidth="1"/>
-    <col min="8" max="8" width="33.6640625" customWidth="1"/>
-    <col min="9" max="9" width="96.1640625" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="35.88"/>
+    <col customWidth="1" min="2" max="2" width="21.25"/>
+    <col customWidth="1" min="3" max="3" width="23.25"/>
+    <col customWidth="1" min="4" max="4" width="49.5"/>
+    <col customWidth="1" min="5" max="5" width="13.88"/>
+    <col customWidth="1" min="6" max="6" width="102.5"/>
+    <col customWidth="1" min="7" max="7" width="33.25"/>
+    <col customWidth="1" min="8" max="8" width="33.75"/>
+    <col customWidth="1" min="9" max="9" width="96.25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -2862,28 +2854,28 @@
       <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2">
       <c r="A2" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B2" s="6">
-        <v>46072</v>
-      </c>
-      <c r="C2" s="7">
-        <v>0.58333333333333337</v>
+      <c r="B2" s="7">
+        <v>46072.0</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.5833333333333334</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>188</v>
@@ -2891,28 +2883,28 @@
       <c r="E2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="9" t="s">
         <v>189</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="10" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3">
       <c r="A3" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B3" s="6">
-        <v>46079</v>
-      </c>
-      <c r="C3" s="7">
-        <v>0.70833333333333337</v>
+      <c r="B3" s="7">
+        <v>46079.0</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.7083333333333334</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>192</v>
@@ -2920,27 +2912,27 @@
       <c r="E3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="9" t="s">
         <v>193</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="10" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4">
       <c r="A4" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B4" s="6">
-        <v>46086</v>
-      </c>
-      <c r="C4" s="7">
+      <c r="B4" s="7">
+        <v>46086.0</v>
+      </c>
+      <c r="C4" s="8">
         <v>0.5</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -2949,28 +2941,28 @@
       <c r="E4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="9" t="s">
         <v>198</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="9" t="s">
         <v>200</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5">
       <c r="A5" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B5" s="6">
-        <v>46101</v>
+      <c r="B5" s="7">
+        <v>46101.0</v>
       </c>
       <c r="C5" s="4">
-        <v>0.72916666666666663</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>202</v>
@@ -2978,25 +2970,25 @@
       <c r="E5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="9" t="s">
         <v>203</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="11" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6">
       <c r="A6" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B6" s="6">
-        <v>46108</v>
+      <c r="B6" s="7">
+        <v>46108.0</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>208</v>
@@ -3007,7 +2999,7 @@
       <c r="E6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="9" t="s">
         <v>210</v>
       </c>
       <c r="G6" s="2" t="s">
@@ -3016,19 +3008,19 @@
       <c r="H6" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="12" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7">
       <c r="A7" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B7" s="11">
-        <v>46085</v>
+      <c r="B7" s="13">
+        <v>46085.0</v>
       </c>
       <c r="C7" s="4">
-        <v>0.70833333333333337</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>214</v>
@@ -3045,19 +3037,19 @@
       <c r="H7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="12" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="11">
-        <v>46086</v>
-      </c>
-      <c r="C8" s="7">
-        <v>0.66666666666666663</v>
+      <c r="B8" s="13">
+        <v>46086.0</v>
+      </c>
+      <c r="C8" s="8">
+        <v>0.6666666666666666</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>35</v>
@@ -3074,21 +3066,21 @@
       <c r="H8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="10" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9">
       <c r="A9" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B9" s="11">
-        <v>46101</v>
+      <c r="B9" s="13">
+        <v>46101.0</v>
       </c>
       <c r="C9" s="4">
         <v>0.75</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="14" t="s">
         <v>222</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -3103,16 +3095,16 @@
       <c r="H9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="11" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10">
       <c r="A10" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B10" s="11">
-        <v>46132</v>
+      <c r="B10" s="13">
+        <v>46132.0</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>35</v>
@@ -3136,12 +3128,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11">
       <c r="A11" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="B11" s="11">
-        <v>46146</v>
+      <c r="B11" s="13">
+        <v>46146.0</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>35</v>
@@ -3165,12 +3157,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12">
       <c r="A12" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="11">
-        <v>46160</v>
+      <c r="B12" s="13">
+        <v>46160.0</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>35</v>
@@ -3194,12 +3186,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13">
       <c r="A13" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="B13" s="11">
-        <v>46174</v>
+      <c r="B13" s="13">
+        <v>46174.0</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>35</v>
@@ -3223,173 +3215,143 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
-      <c r="A14" s="13" t="s">
+    <row r="14">
+      <c r="A14" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="B14" s="14">
-        <v>46086</v>
-      </c>
-      <c r="C14" s="15">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="D14" s="16" t="s">
+      <c r="B14" s="16">
+        <v>46086.0</v>
+      </c>
+      <c r="C14" s="17">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="D14" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F14" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="H14" s="18" t="s">
+      <c r="H14" s="21" t="s">
         <v>235</v>
       </c>
-      <c r="I14" s="19" t="s">
+      <c r="I14" s="22" t="s">
         <v>236</v>
       </c>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
-      <c r="P14" s="13"/>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="13"/>
-      <c r="S14" s="13"/>
-      <c r="T14" s="13"/>
-      <c r="U14" s="13"/>
-      <c r="V14" s="13"/>
-      <c r="W14" s="13"/>
-      <c r="X14" s="13"/>
-      <c r="Y14" s="13"/>
-      <c r="Z14" s="13"/>
-    </row>
-    <row r="15" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A15" s="13" t="s">
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15"/>
+      <c r="R14" s="15"/>
+      <c r="S14" s="15"/>
+      <c r="T14" s="15"/>
+      <c r="U14" s="15"/>
+      <c r="V14" s="15"/>
+      <c r="W14" s="15"/>
+      <c r="X14" s="15"/>
+      <c r="Y14" s="15"/>
+      <c r="Z14" s="15"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="B15" s="14">
-        <v>46098</v>
-      </c>
-      <c r="C15" s="20">
+      <c r="B15" s="16">
+        <v>46098.0</v>
+      </c>
+      <c r="C15" s="23">
         <v>0.75</v>
       </c>
-      <c r="D15" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" s="13" t="s">
+      <c r="D15" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="F15" s="21" t="s">
+      <c r="F15" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="G15" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="H15" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="I15" s="23" t="s">
+      <c r="H15" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="13"/>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13"/>
-      <c r="T15" s="13"/>
-      <c r="U15" s="13"/>
-      <c r="V15" s="13"/>
-      <c r="W15" s="13"/>
-      <c r="X15" s="13"/>
-      <c r="Y15" s="13"/>
-      <c r="Z15" s="13"/>
-    </row>
-    <row r="16" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A16" s="24" t="s">
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="15"/>
+      <c r="R15" s="15"/>
+      <c r="S15" s="15"/>
+      <c r="T15" s="15"/>
+      <c r="U15" s="15"/>
+      <c r="V15" s="15"/>
+      <c r="W15" s="15"/>
+      <c r="X15" s="15"/>
+      <c r="Y15" s="15"/>
+      <c r="Z15" s="15"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="s">
         <v>240</v>
       </c>
-      <c r="B16" s="25">
-        <v>46130</v>
-      </c>
-      <c r="C16" s="24" t="s">
+      <c r="B16" s="28">
+        <v>46130.0</v>
+      </c>
+      <c r="C16" s="29">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="E16" s="27" t="s">
         <v>241</v>
       </c>
-      <c r="D16" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="E16" s="24" t="s">
+      <c r="F16" s="30" t="s">
         <v>242</v>
       </c>
-      <c r="F16" s="26" t="s">
+      <c r="G16" s="27" t="s">
         <v>243</v>
       </c>
-      <c r="G16" s="24" t="s">
+      <c r="H16" s="27" t="s">
         <v>244</v>
       </c>
-      <c r="H16" s="24" t="s">
+      <c r="I16" s="31" t="s">
         <v>245</v>
       </c>
-      <c r="I16" s="27" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A17" s="24" t="s">
-        <v>247</v>
-      </c>
-      <c r="B17" s="28">
-        <v>46142</v>
-      </c>
-      <c r="C17" s="20">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="E17" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>249</v>
-      </c>
-      <c r="G17" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="H17" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="I17" s="29" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="15.75" customHeight="1">
-      <c r="F18" s="17"/>
+    </row>
+    <row r="17">
+      <c r="F17" s="32"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
-    <hyperlink ref="I3" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
-    <hyperlink ref="I5" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
-    <hyperlink ref="I6" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
-    <hyperlink ref="I7" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
-    <hyperlink ref="I8" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000005000000}"/>
-    <hyperlink ref="I9" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
-    <hyperlink ref="I14" r:id="rId8" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
-    <hyperlink ref="I15" r:id="rId9" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
-    <hyperlink ref="I16" r:id="rId10" xr:uid="{00000000-0004-0000-0200-000009000000}"/>
-    <hyperlink ref="I17" r:id="rId11" xr:uid="{00000000-0004-0000-0200-00000A000000}"/>
+    <hyperlink r:id="rId1" ref="I2"/>
+    <hyperlink r:id="rId2" ref="I3"/>
+    <hyperlink r:id="rId3" ref="I5"/>
+    <hyperlink r:id="rId4" ref="I6"/>
+    <hyperlink r:id="rId5" ref="I7"/>
+    <hyperlink r:id="rId6" ref="I8"/>
+    <hyperlink r:id="rId7" ref="I9"/>
+    <hyperlink r:id="rId8" ref="I14"/>
+    <hyperlink r:id="rId9" ref="I15"/>
+    <hyperlink r:id="rId10" ref="I16"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId11"/>
 </worksheet>
 </file>